--- a/data/trans_dic/P19F$tarde-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19F$tarde-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la tarde</t>
+          <t>Población que, al menos, se cepilla los dientes por la tarde (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,37; 36,0</t>
+          <t>22,82; 36,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,06; 42,98</t>
+          <t>27,46; 43,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,87; 36,59</t>
+          <t>25,85; 36,38</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,32; 43,88</t>
+          <t>29,66; 43,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,6; 46,44</t>
+          <t>31,36; 45,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,76; 43,39</t>
+          <t>32,8; 42,98</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,29; 36,4</t>
+          <t>25,45; 36,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,06; 35,01</t>
+          <t>15,65; 34,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,94; 34,53</t>
+          <t>24,45; 34,13</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,79; 34,13</t>
+          <t>26,85; 34,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,49; 37,21</t>
+          <t>28,23; 37,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,49; 34,17</t>
+          <t>28,09; 34,23</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,0; 33,86</t>
+          <t>24,19; 33,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,01; 34,88</t>
+          <t>26,23; 35,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,37; 32,81</t>
+          <t>26,4; 32,97</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24,9; 40,36</t>
+          <t>24,96; 39,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,31; 35,27</t>
+          <t>27,04; 35,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27,82; 35,06</t>
+          <t>27,5; 34,74</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,56; 32,96</t>
+          <t>28,55; 33,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29,96; 34,24</t>
+          <t>30,05; 34,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,78; 32,97</t>
+          <t>29,89; 32,93</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la tarde</t>
+          <t>Población que, al menos, se cepilla los dientes por la tarde (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>44684; 71921</t>
+          <t>45589; 73228</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34869; 55371</t>
+          <t>35382; 55933</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85003; 120244</t>
+          <t>84934; 119542</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52539; 78613</t>
+          <t>53138; 78758</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56711; 83333</t>
+          <t>56269; 82192</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>117491; 155618</t>
+          <t>117611; 154128</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>71346; 102685</t>
+          <t>71797; 101978</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11973; 26106</t>
+          <t>11669; 26066</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85368; 123157</t>
+          <t>87190; 121731</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>166801; 212494</t>
+          <t>167179; 213796</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>120413; 157300</t>
+          <t>119345; 156660</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>297839; 357238</t>
+          <t>293675; 357849</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>80890; 114134</t>
+          <t>81542; 114077</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>105285; 141227</t>
+          <t>106197; 142958</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>195604; 243427</t>
+          <t>195825; 244590</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>39081; 63345</t>
+          <t>39173; 62059</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>144114; 186128</t>
+          <t>142677; 186187</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>190474; 240041</t>
+          <t>188247; 237875</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>507738; 585875</t>
+          <t>507483; 589165</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>520730; 595212</t>
+          <t>522352; 598564</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1047161; 1159030</t>
+          <t>1050727; 1157572</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19F$tarde-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19F$tarde-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,82; 36,66</t>
+          <t>22,87; 35,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,46; 43,41</t>
+          <t>26,92; 43,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,85; 36,38</t>
+          <t>25,98; 36,46</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,66; 43,96</t>
+          <t>29,53; 44,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,36; 45,8</t>
+          <t>31,19; 46,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,8; 42,98</t>
+          <t>32,95; 42,8</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,45; 36,15</t>
+          <t>25,25; 36,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,65; 34,96</t>
+          <t>14,87; 34,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,45; 34,13</t>
+          <t>24,95; 34,75</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,85; 34,33</t>
+          <t>26,4; 33,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,23; 37,06</t>
+          <t>28,0; 36,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,09; 34,23</t>
+          <t>28,59; 34,36</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,19; 33,85</t>
+          <t>23,77; 33,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,23; 35,31</t>
+          <t>26,04; 35,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,4; 32,97</t>
+          <t>26,23; 33,33</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24,96; 39,54</t>
+          <t>24,8; 39,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,04; 35,28</t>
+          <t>27,34; 35,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27,5; 34,74</t>
+          <t>27,71; 35,15</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,55; 33,14</t>
+          <t>28,54; 33,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30,05; 34,44</t>
+          <t>29,69; 34,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,89; 32,93</t>
+          <t>29,9; 33,13</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>45589; 73228</t>
+          <t>45676; 71323</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35382; 55933</t>
+          <t>34680; 55428</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84934; 119542</t>
+          <t>85353; 119813</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53138; 78758</t>
+          <t>52912; 79139</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56269; 82192</t>
+          <t>55977; 83973</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>117611; 154128</t>
+          <t>118175; 153501</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>71797; 101978</t>
+          <t>71227; 102397</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11669; 26066</t>
+          <t>11090; 25584</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87190; 121731</t>
+          <t>88974; 123937</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>167179; 213796</t>
+          <t>164381; 211462</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>119345; 156660</t>
+          <t>118339; 155759</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>293675; 357849</t>
+          <t>298926; 359164</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>81542; 114077</t>
+          <t>80109; 113638</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>106197; 142958</t>
+          <t>105418; 144593</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>195825; 244590</t>
+          <t>194613; 247288</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>39173; 62059</t>
+          <t>38922; 62299</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>142677; 186187</t>
+          <t>144261; 187071</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>188247; 237875</t>
+          <t>189678; 240674</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>507483; 589165</t>
+          <t>507409; 588280</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>522352; 598564</t>
+          <t>515998; 597846</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1050727; 1157572</t>
+          <t>1051174; 1164640</t>
         </is>
       </c>
     </row>
